--- a/docs/test/unit/NOUS-97/観点表_worldService.xlsx
+++ b/docs/test/unit/NOUS-97/観点表_worldService.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>B2-F, B3-T</t>
+          <t>B2-F, B3-T, B3-F</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>B8-F, B11-F, B12-F</t>
+          <t>B1-F, B8-F, B11-F, B12-F</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>B14-F, B6-T, B7-F</t>
+          <t>B14-F, B6-T, B7-F, B13-F</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>B8-F, B11-F, B12-F</t>
+          <t>B1-F, B8-F, B11-F, B12-F</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
